--- a/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A469F82-2101-4A6A-84BC-0C752C2CD0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9343FD-2A61-4CF7-884C-1CB37731FE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9343FD-2A61-4CF7-884C-1CB37731FE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C33E86E-7954-46B8-8564-AEC6191C7EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="設定値" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー指摘一覧!$A$1:$O$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー指摘一覧!$A$1:$O$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー実施状況!$A$1:$S$17</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">設定値!$A$1:$AQ$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">レビュー指摘一覧!$3:$4</definedName>
@@ -1381,7 +1381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="212">
   <si>
     <t>レビュー対象物</t>
     <rPh sb="4" eb="7">
@@ -2597,15 +2597,7 @@
     <t>山田　太郎</t>
   </si>
   <si>
-    <t xml:space="preserve">_x000D_
-</t>
-  </si>
-  <si>
-    <t>鈴木　花子</t>
-  </si>
-  <si>
-    <t>山田　太郎</t>
-    <phoneticPr fontId="2"/>
+    <t>01_要件漏れ</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
@@ -2613,34 +2605,34 @@
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。_x000D_
 ※レビュー日時を書く場合はコロンの直後に*を書く。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 </t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>鈴木　花子</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>02_要件誤り</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容の例。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容はデリミタ（---）の後に記入する。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11_機能・仕様漏れ</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容を確認し、指摘をクローズする例。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
@@ -2648,78 +2640,36 @@
 「済」の前にスペースを空けて確認日と確認者を書くこともできる。_x000D_
 08/02山田 済_x000D_
 </t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>08/02山田</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12_機能・仕様誤り</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 機能・仕様誤りの指摘例（カテゴリd）。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>21_設計・ドキュメント規約違反</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 設計・ドキュメント規約違反の指摘例（カテゴリe）。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>22_記述誤り</t>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 記述誤りの指摘例（カテゴリf）。_x000D_
 </t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>91_疑問点、確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-疑問点・確認の指摘例（カテゴリg）。_x000D_
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-改善要望の指摘例（カテゴリh）。_x000D_
-</t>
-  </si>
-  <si>
-    <t>93_仕様変更</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-仕様変更の指摘例（カテゴリi）。_x000D_
-</t>
-  </si>
-  <si>
-    <t>94_テスト項目漏れ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-テスト項目漏れの指摘例（カテゴリj）。_x000D_
-</t>
-  </si>
-  <si>
-    <t>95_テスト漏れ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-テスト漏れの指摘例（カテゴリk）。_x000D_
-</t>
-  </si>
-  <si>
-    <t>96_その他</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-その他の指摘例（カテゴリl）。_x000D_
-</t>
   </si>
   <si>
     <t>詳細設計</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4817,7 +4767,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="90" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D1" s="91"/>
       <c r="E1" s="100" t="s">
@@ -4989,8 +4939,8 @@
       <c r="B7" s="156"/>
       <c r="C7" s="157"/>
       <c r="D7" s="85">
-        <f>COUNTA(レビュー指摘一覧!H5:H10002)</f>
-        <v>12</v>
+        <f>COUNTA(レビュー指摘一覧!H5:H9996)</f>
+        <v>6</v>
       </c>
       <c r="E7" s="161"/>
       <c r="F7" s="76" t="s">
@@ -4999,7 +4949,7 @@
       <c r="G7" s="156"/>
       <c r="H7" s="157"/>
       <c r="I7" s="85">
-        <f>COUNTIF(レビュー指摘一覧!K5:K10002,"01_要")</f>
+        <f>COUNTIF(レビュー指摘一覧!K5:K9996,"01_要")</f>
         <v>0</v>
       </c>
       <c r="J7" s="84"/>
@@ -5248,12 +5198,12 @@
         <v>0</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -5449,7 +5399,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="2" customWidth="1"/>
@@ -5542,25 +5492,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
       <c r="H5" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I5" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J5" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="J5" s="27" t="s">
-        <v>198</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="28"/>
       <c r="M5" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="31"/>
@@ -5574,25 +5524,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J6" s="27" t="s">
         <v>200</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>201</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="28"/>
       <c r="M6" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="31"/>
@@ -5606,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -5616,7 +5566,7 @@
         <v>202</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J7" s="27" t="s">
         <v>203</v>
@@ -5624,7 +5574,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N7" s="30"/>
       <c r="O7" s="31" t="s">
@@ -5640,25 +5590,25 @@
         <v>1</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="H8" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I8" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J8" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>198</v>
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="28"/>
       <c r="M8" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="31"/>
@@ -5672,25 +5622,25 @@
         <v>1</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
       <c r="H9" s="27" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I9" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J9" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>198</v>
       </c>
       <c r="K9" s="26"/>
       <c r="L9" s="28"/>
       <c r="M9" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N9" s="30"/>
       <c r="O9" s="31"/>
@@ -5704,261 +5654,69 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
       <c r="H10" s="27" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I10" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J10" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="J10" s="27" t="s">
-        <v>198</v>
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="28"/>
       <c r="M10" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N10" s="30"/>
       <c r="O10" s="31"/>
     </row>
-    <row r="11" spans="1:15" ht="47.25">
+    <row r="11" spans="1:15" ht="60" customHeight="1">
       <c r="A11" s="67">
         <f>ROW()-4</f>
         <v>7</v>
       </c>
-      <c r="B11" s="24">
-        <v>1</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>208</v>
-      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
-      <c r="H11" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J11" s="27" t="s">
-        <v>194</v>
-      </c>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="29"/>
       <c r="K11" s="26"/>
       <c r="L11" s="28"/>
-      <c r="M11" s="28" t="s">
-        <v>195</v>
-      </c>
+      <c r="M11" s="28"/>
       <c r="N11" s="30"/>
       <c r="O11" s="31"/>
     </row>
-    <row r="12" spans="1:15" ht="47.25">
-      <c r="A12" s="67">
-        <f>ROW()-4</f>
-        <v>8</v>
-      </c>
-      <c r="B12" s="24">
-        <v>1</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J12" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N12" s="30"/>
-      <c r="O12" s="31"/>
-    </row>
-    <row r="13" spans="1:15" ht="47.25">
-      <c r="A13" s="67">
-        <f>ROW()-4</f>
-        <v>9</v>
-      </c>
-      <c r="B13" s="24">
-        <v>1</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J13" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N13" s="30"/>
-      <c r="O13" s="31"/>
-    </row>
-    <row r="14" spans="1:15" ht="47.25">
-      <c r="A14" s="67">
-        <f>ROW()-4</f>
-        <v>10</v>
-      </c>
-      <c r="B14" s="24">
-        <v>1</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J14" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N14" s="30"/>
-      <c r="O14" s="31"/>
-    </row>
-    <row r="15" spans="1:15" ht="47.25">
-      <c r="A15" s="67">
-        <f>ROW()-4</f>
-        <v>11</v>
-      </c>
-      <c r="B15" s="24">
-        <v>1</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J15" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N15" s="30"/>
-      <c r="O15" s="31"/>
-    </row>
-    <row r="16" spans="1:15" ht="47.25">
-      <c r="A16" s="67">
-        <f>ROW()-4</f>
-        <v>12</v>
-      </c>
-      <c r="B16" s="24">
-        <v>1</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J16" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N16" s="30"/>
-      <c r="O16" s="31"/>
-    </row>
-    <row r="17" spans="1:15" ht="60" customHeight="1">
-      <c r="A17" s="67">
-        <f>ROW()-4</f>
-        <v>13</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="31"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="51" t="s">
+    <row r="12" spans="1:15">
+      <c r="A12" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B12" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="68"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -5978,26 +5736,26 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations xWindow="228" yWindow="361" count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L17" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"〇"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5:C17" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5:C11" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>指摘分類</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F17" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F11" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>レビュー検知漏れ原因</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="項目値が規定範囲外です" error="項目に適した値の再入力をお願いします。_x000a_詳しくは「影響」欄にマウスポインタを移動し、表示されるコメントを参照して下さい。" sqref="G5:G17" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="項目値が規定範囲外です" error="項目に適した値の再入力をお願いします。_x000a_詳しくは「影響」欄にマウスポインタを移動し、表示されるコメントを参照して下さい。" sqref="G5:G11" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>影響度</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B5:B17" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="対処要否を選択してください。" prompt="01_要_x000a_02_不要_x000a_03_重複_x000a_99_判断できず（TL判断要）" sqref="K5:K17" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B5:B11" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="対処要否を選択してください。" prompt="01_要_x000a_02_不要_x000a_03_重複_x000a_99_判断できず（TL判断要）" sqref="K5:K11" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>対処要否</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D5:D17" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D5:D11" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>原因分類</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="項目値が規定範囲外です" error="項目に適した値の再入力をお願いします。_x000a_詳しくは「原因」欄にマウスポインタを移動し、表示されるコメントを参照して下さい。" promptTitle="原因工程を選択してください。" prompt="01_要件定義_x000a_02_外部設計_x000a_03_内部設計_x000a_04_プログラミング_x000a_05_サブシステム内結合テスト_x000a_06_サブシステム間結合テスト_x000a_07_システムテスト_x000a_11_インフラ運用要件定義_x000a_12_インフラ運用設計_x000a_13_インフラ運用構築_x000a_14_インフラ運用テスト_x000a_21_移行・展開_x000a_99_判断できず（TL判断要）" sqref="E5:E17" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="項目値が規定範囲外です" error="項目に適した値の再入力をお願いします。_x000a_詳しくは「原因」欄にマウスポインタを移動し、表示されるコメントを参照して下さい。" promptTitle="原因工程を選択してください。" prompt="01_要件定義_x000a_02_外部設計_x000a_03_内部設計_x000a_04_プログラミング_x000a_05_サブシステム内結合テスト_x000a_06_サブシステム間結合テスト_x000a_07_システムテスト_x000a_11_インフラ運用要件定義_x000a_12_インフラ運用設計_x000a_13_インフラ運用構築_x000a_14_インフラ運用テスト_x000a_21_移行・展開_x000a_99_判断できず（TL判断要）" sqref="E5:E11" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>原因工程</formula1>
     </dataValidation>
   </dataValidations>
